--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126674241</v>
       </c>
       <c r="B2" t="n">
-        <v>95682</v>
+        <v>95757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126674241</v>
       </c>
       <c r="B2" t="n">
-        <v>95757</v>
+        <v>95763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126674241</v>
       </c>
       <c r="B2" t="n">
-        <v>95763</v>
+        <v>95764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>126669415</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>126669415</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126674241</v>
       </c>
       <c r="B2" t="n">
-        <v>95764</v>
+        <v>95757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>126669415</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>126669415</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,6 +1613,800 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133547414</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58291</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592377</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6320812</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133547589</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58044</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592377</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6320812</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133551418</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592449</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6320848</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133547747</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96718</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592377</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6320812</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133547427</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592377</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6320812</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133551095</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96718</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592372</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6320707</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133551358</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592449</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6320848</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1966,7 +1966,7 @@
         <v>133547747</v>
       </c>
       <c r="B13" t="n">
-        <v>96718</v>
+        <v>96720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>133551095</v>
       </c>
       <c r="B15" t="n">
-        <v>96718</v>
+        <v>96720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -1966,7 +1966,7 @@
         <v>133547747</v>
       </c>
       <c r="B13" t="n">
-        <v>96720</v>
+        <v>96728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>133551095</v>
       </c>
       <c r="B15" t="n">
-        <v>96720</v>
+        <v>96728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126674241</v>
+        <v>133547747</v>
       </c>
       <c r="B2" t="n">
-        <v>95764</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ävjevik, Ävjevik, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592514</v>
+        <v>592377</v>
       </c>
       <c r="R2" t="n">
-        <v>6320734</v>
+        <v>6320812</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,69 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126669850</v>
+        <v>133551095</v>
       </c>
       <c r="B3" t="n">
-        <v>57603</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aleholmen, Aleholmen, Sm</t>
+          <t>Korshamn, Korshamn, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592368</v>
+        <v>592372</v>
       </c>
       <c r="R3" t="n">
-        <v>6320787</v>
+        <v>6320707</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,62 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126670323</v>
+        <v>126674241</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Ävjevik, Ävjevik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592392</v>
+        <v>592514</v>
       </c>
       <c r="R4" t="n">
-        <v>6320717</v>
+        <v>6320734</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126669402</v>
+        <v>126674427</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ävjevik, Ävjevik, Sm</t>
+          <t>Aleholmen, Aleholmen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592389</v>
+        <v>592295</v>
       </c>
       <c r="R5" t="n">
-        <v>6320834</v>
+        <v>6320808</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1114,72 +1081,76 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126692440</v>
+        <v>126669415</v>
       </c>
       <c r="B6" t="n">
-        <v>57787</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Ävjevik, Björnö, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592302</v>
+        <v>592390</v>
       </c>
       <c r="R6" t="n">
-        <v>6320843</v>
+        <v>6320835</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,27 +1216,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126692336</v>
+        <v>126670551</v>
       </c>
       <c r="B7" t="n">
-        <v>57603</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1273,36 +1244,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1K+</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Korshamnsgrundet, Korshamnsgrundet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592361</v>
+        <v>592453</v>
       </c>
       <c r="R7" t="n">
-        <v>6320775</v>
+        <v>6320658</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,24 +1289,9 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ungfågel, fjäderrester av en havsörn</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,26 +1306,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126669415</v>
+        <v>130961747</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1401,36 +1346,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ävjevik, Björnö, Mönsterås, Sm</t>
+          <t>Ävjevik, Ävjevik, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592390</v>
+        <v>592313</v>
       </c>
       <c r="R8" t="n">
-        <v>6320835</v>
+        <v>6320955</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,22 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,12 +1408,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1499,11 +1423,11 @@
         <v>131146223</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1615,27 +1539,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133547414</v>
+        <v>126669850</v>
       </c>
       <c r="B10" t="n">
-        <v>58308</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1645,27 +1569,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>dödad av predator</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Aleholmen, Aleholmen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592377</v>
+        <v>592368</v>
       </c>
       <c r="R10" t="n">
-        <v>6320812</v>
+        <v>6320787</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,22 +1618,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,17 +1653,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133547589</v>
+        <v>126692336</v>
       </c>
       <c r="B11" t="n">
-        <v>58061</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,21 +1671,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102626</v>
+        <v>100067</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,21 +1693,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Korshamn, Björnö, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592377</v>
+        <v>592361</v>
       </c>
       <c r="R11" t="n">
-        <v>6320812</v>
+        <v>6320775</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,22 +1741,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ungfågel, fjäderrester av en havsörn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,39 +1781,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133551418</v>
+        <v>133547589</v>
       </c>
       <c r="B12" t="n">
-        <v>58461</v>
+        <v>58061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103018</v>
+        <v>102626</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1882,7 +1823,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1891,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592449</v>
+        <v>592377</v>
       </c>
       <c r="R12" t="n">
-        <v>6320848</v>
+        <v>6320812</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1956,17 +1897,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133547747</v>
+        <v>133547414</v>
       </c>
       <c r="B13" t="n">
-        <v>96769</v>
+        <v>58308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,27 +1915,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>103008</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2186,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133551095</v>
+        <v>79413502</v>
       </c>
       <c r="B15" t="n">
-        <v>96769</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,34 +2147,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korshamn, Korshamn, Sm</t>
+          <t>Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592372</v>
+        <v>592466</v>
       </c>
       <c r="R15" t="n">
-        <v>6320707</v>
+        <v>6320685</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2251,22 +2208,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,22 +2238,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Håkan Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Håkan Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133551358</v>
+        <v>126669402</v>
       </c>
       <c r="B16" t="n">
-        <v>58658</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,16 +2261,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2321,29 +2278,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+          <t>Ävjevik, Ävjevik, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592449</v>
+        <v>592389</v>
       </c>
       <c r="R16" t="n">
-        <v>6320848</v>
+        <v>6320834</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,22 +2320,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,15 +2340,717 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133551418</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592449</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6320848</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Jan Brenander</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Jan Brenander</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>79413501</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592466</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6320685</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126670323</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korshamn, Korshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592392</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6320717</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133547495</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592377</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6320812</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133551358</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592449</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6320848</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126692440</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Korshamn, Björnö, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592302</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6320843</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31889-2025 artfynd.xlsx
+++ b/artfynd/A 31889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133547747</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133551095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674241</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674427</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670551</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961747</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131146223</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669850</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126692336</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1901,6 +1956,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133547589</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2017,6 +2077,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133547414</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2133,6 +2198,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133547427</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79413502</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126669402</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2465,6 +2545,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133551418</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2579,6 +2664,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79413501</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670323</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2816,6 +2911,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133547495</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2932,6 +3032,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133551358</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3051,8 +3156,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126692440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>